--- a/docs/package/out/BrokerVerse_Test_Cases.xlsx
+++ b/docs/package/out/BrokerVerse_Test_Cases.xlsx
@@ -5246,17 +5246,17 @@
       </c>
       <c r="L35" s="19" t="inlineStr">
         <is>
-          <t>No consent capture on the client or prospect screens.</t>
+          <t>Client Data privacy tab and the privacy API record consent per purpose (processing, marketing, sharing) with channel, evidence and notice version; the consent is shown on the client with its history. Re-test: consent for marketing recorded on CL-2026-00068 (201) and read back.</t>
         </is>
       </c>
       <c r="M35" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>BV-DEF-002</t>
+          <t>BV-DEF-002 (closed)</t>
         </is>
       </c>
       <c r="O35" s="19" t="inlineStr">
@@ -5269,7 +5269,11 @@
           <t>03 October 2026</t>
         </is>
       </c>
-      <c r="Q35" s="19" t="inlineStr"/>
+      <c r="Q35" s="19" t="inlineStr">
+        <is>
+          <t>Re-test of 03 October 2026 after the fix, fresh database with the UAT data set.</t>
+        </is>
+      </c>
       <c r="R35" s="19" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5331,17 +5335,17 @@
       </c>
       <c r="L36" s="19" t="inlineStr">
         <is>
-          <t>No data subject request register and no anonymisation function in this release.</t>
+          <t>Master &gt; Data Privacy: request DSR-2026-00001 logged, due 15 days after receipt (18/10/2026); personal data export produced; anonymise dry run refuses a client with a policy in force and lists the reasons.</t>
         </is>
       </c>
       <c r="M36" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>BV-DEF-002</t>
+          <t>BV-DEF-002 (closed)</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -5354,7 +5358,11 @@
           <t>03 October 2026</t>
         </is>
       </c>
-      <c r="Q36" s="19" t="inlineStr"/>
+      <c r="Q36" s="19" t="inlineStr">
+        <is>
+          <t>Re-test of 03 October 2026 after the fix, fresh database with the UAT data set.</t>
+        </is>
+      </c>
       <c r="R36" s="19" t="inlineStr"/>
     </row>
     <row r="37">
@@ -8391,17 +8399,17 @@
       </c>
       <c r="L71" s="19" t="inlineStr">
         <is>
-          <t>Rules and LGU rates saved by Accounting; Sales refused. Signed in as Accounting, the product drop-down of the charges calculator stays empty: the screen request for placement options is refused (403).</t>
+          <t>Rules and LGU rates saved by Accounting; Sales refused. Signed in as Accounting, the screen loads with no refused request and the product list of the charges calculator is filled.</t>
         </is>
       </c>
       <c r="M71" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>BV-DEF-006</t>
+          <t>BV-DEF-006 (closed)</t>
         </is>
       </c>
       <c r="O71" s="19" t="inlineStr">
@@ -8414,7 +8422,11 @@
           <t>03 October 2026</t>
         </is>
       </c>
-      <c r="Q71" s="19" t="inlineStr"/>
+      <c r="Q71" s="19" t="inlineStr">
+        <is>
+          <t>Re-test of 03 October 2026 after the fix, fresh database with the UAT data set.</t>
+        </is>
+      </c>
       <c r="R71" s="19" t="inlineStr">
         <is>
           <t>backend/test/premium-charges.test.js :: lets Accounting maintain rules and LGU rates; Sales cannot [passed]
@@ -10469,17 +10481,17 @@
       </c>
       <c r="L95" s="19" t="inlineStr">
         <is>
-          <t>The component list does not show the template; the same factor name appears several times and looks duplicated.</t>
+          <t>Rating Engine, Coverage Builder, Acceptance Rules and Document Manager lists show a Template column; the same factor code on two templates (VEH_AGE on MOT-003-2025 and MOTOR-COMP-2026) is now distinguishable.</t>
         </is>
       </c>
       <c r="M95" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>BV-DEF-004</t>
+          <t>BV-DEF-004 (closed)</t>
         </is>
       </c>
       <c r="O95" s="19" t="inlineStr">
@@ -10492,7 +10504,11 @@
           <t>03 October 2026</t>
         </is>
       </c>
-      <c r="Q95" s="19" t="inlineStr"/>
+      <c r="Q95" s="19" t="inlineStr">
+        <is>
+          <t>Re-test of 03 October 2026 after the fix, fresh database with the UAT data set.</t>
+        </is>
+      </c>
       <c r="R95" s="19" t="inlineStr">
         <is>
           <t>Screen check /product-configurator/rating: opened clean</t>
@@ -44996,17 +45012,17 @@
       </c>
       <c r="L495" s="19" t="inlineStr">
         <is>
-          <t>91 screens opened; problems: Accounts &gt; Incentive &gt; My Programs: 1 element(s) clipped at 1440 px / Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates: failed API call 403 GET /placements/options, console error: Failed to load resource: the server responded with a status of 403 (Forbidden)</t>
+          <t>96 screens opened as liza.quiambao at 1440 px: no refused request, no console error, no clipped element, no horizontal scroll.</t>
         </is>
       </c>
       <c r="M495" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N495" s="19" t="inlineStr">
         <is>
-          <t>BV-DEF-006, BV-OBS-008</t>
+          <t>BV-DEF-006, BV-OBS-008 (closed)</t>
         </is>
       </c>
       <c r="O495" s="19" t="inlineStr">
@@ -45019,7 +45035,11 @@
           <t>03 October 2026</t>
         </is>
       </c>
-      <c r="Q495" s="19" t="inlineStr"/>
+      <c r="Q495" s="19" t="inlineStr">
+        <is>
+          <t>Re-test of 03 October 2026 after the fix, fresh database with the UAT data set.</t>
+        </is>
+      </c>
       <c r="R495" s="19" t="inlineStr">
         <is>
           <t>Screen check of 03 October 2026 (Chromium, 1440 x 900): access, console errors, failed API calls and clipped content per menu screen, user Accounting Officer (liza.quiambao)</t>
@@ -45267,17 +45287,17 @@
       </c>
       <c r="L498" s="19" t="inlineStr">
         <is>
-          <t>91 screens opened; problems: Accounts &gt; Incentive &gt; My Programs: 1 element(s) clipped at 1440 px / Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates: failed API call 403 GET /placements/options, console error: Failed to load resource: the server responded with a status of 403 (Forbidden)</t>
+          <t>96 screens opened as teresa.villaroman at 1440 px: no refused request, no console error, no clipped element, no horizontal scroll.</t>
         </is>
       </c>
       <c r="M498" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N498" s="19" t="inlineStr">
         <is>
-          <t>BV-DEF-006, BV-OBS-008</t>
+          <t>BV-DEF-006, BV-OBS-008 (closed)</t>
         </is>
       </c>
       <c r="O498" s="19" t="inlineStr">
@@ -45290,7 +45310,11 @@
           <t>03 October 2026</t>
         </is>
       </c>
-      <c r="Q498" s="19" t="inlineStr"/>
+      <c r="Q498" s="19" t="inlineStr">
+        <is>
+          <t>Re-test of 03 October 2026 after the fix, fresh database with the UAT data set.</t>
+        </is>
+      </c>
       <c r="R498" s="19" t="inlineStr">
         <is>
           <t>Screen check of 03 October 2026 (Chromium, 1440 x 900): access, console errors, failed API calls and clipped content per menu screen, user Accounting Manager (teresa.villaroman)</t>
@@ -46656,7 +46680,7 @@
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr"/>
@@ -46684,7 +46708,7 @@
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr"/>
@@ -48192,7 +48216,7 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -49156,7 +49180,7 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr"/>
@@ -65852,7 +65876,7 @@
       </c>
       <c r="D495" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E495" s="19" t="inlineStr"/>
@@ -65978,7 +66002,7 @@
       </c>
       <c r="D498" s="19" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E498" s="19" t="inlineStr"/>
@@ -66164,7 +66188,7 @@
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F3" s="19" t="inlineStr">
@@ -66184,7 +66208,7 @@
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
-          <t>Product backlog; to be scheduled with the client</t>
+          <t>Closed: fixed on 03 October 2026 (Master &gt; Data Privacy, client Data privacy tab); re-tested BV-SEC-034 and BV-SEC-035</t>
         </is>
       </c>
       <c r="J3" s="19" t="inlineStr">
@@ -66268,7 +66292,7 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -66288,7 +66312,7 @@
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>Next minor release</t>
+          <t>Closed: fixed on 03 October 2026 (Template column on the component lists); re-tested BV-PCF-005</t>
         </is>
       </c>
       <c r="J5" s="19" t="inlineStr">
@@ -66320,7 +66344,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
@@ -66340,7 +66364,7 @@
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>No change planned; confirm the window settings with the client at configuration</t>
+          <t>Closed: by design; window settings confirmed with the client at configuration</t>
         </is>
       </c>
       <c r="J6" s="19" t="inlineStr">
@@ -66372,7 +66396,7 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr">
@@ -66392,7 +66416,7 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>Next patch: let the screen read the product list through a permission Accounting holds</t>
+          <t>Closed: fixed on 03 October 2026 (screen reads the product list with a permission Accounting holds); re-tested BV-MST-019, BV-RBA-016, BV-RBA-019</t>
         </is>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -66424,7 +66448,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
@@ -66444,7 +66468,7 @@
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>Next minor release: remove the address from the group or open the Company screen</t>
+          <t>Closed: fixed on 03 October 2026 (menu groups carry no address)</t>
         </is>
       </c>
       <c r="J8" s="19" t="inlineStr">
@@ -66476,7 +66500,7 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
@@ -66496,7 +66520,7 @@
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>Next minor release</t>
+          <t>Closed: fixed on 03 October 2026 (card fits at 1440 px); re-tested BV-RBA-016 and BV-RBA-019</t>
         </is>
       </c>
       <c r="J9" s="19" t="inlineStr">
